--- a/human_resources_forms/001_online_interview_questionnaire_form--human_resources_forms.xlsx
+++ b/human_resources_forms/001_online_interview_questionnaire_form--human_resources_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,8 +441,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -796,12 +796,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>job_satisfaction</t>
+          <t>job_satisfaction_2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Job Satisfaction</t>
+          <t>Job Satisfaction 2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -957,12 +957,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>job_performance</t>
+          <t>job_performance_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Job Performance</t>
+          <t>Job Performance 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -980,12 +980,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>job_performance_reviews</t>
+          <t>job_performance_reviews_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Job Performance Reviews</t>
+          <t>Job Performance Reviews 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>job_performance_reviews</t>
+          <t>job_performance_reviews_3</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Job Performance Reviews</t>
+          <t>Job Performance Reviews 3</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>job_performance_ratings</t>
+          <t>job_performance_ratings_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Job Performance Ratings</t>
+          <t>Job Performance Ratings 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1101,7 +1101,7 @@
   <dimension ref="A1:C35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="33" customWidth="1" min="1" max="1"/>
+    <col width="35" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1398,7 +1398,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>job_satisfaction_choices</t>
+          <t>job_satisfaction_2_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1415,7 +1415,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>job_satisfaction_choices</t>
+          <t>job_satisfaction_2_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1534,7 +1534,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>job_performance_choices</t>
+          <t>job_performance_2_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1551,7 +1551,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>job_performance_choices</t>
+          <t>job_performance_2_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1568,7 +1568,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>job_performance_reviews_choices</t>
+          <t>job_performance_reviews_2_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1585,7 +1585,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>job_performance_reviews_choices</t>
+          <t>job_performance_reviews_2_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1636,7 +1636,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>job_performance_reviews_choices</t>
+          <t>job_performance_reviews_3_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1653,7 +1653,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>job_performance_reviews_choices</t>
+          <t>job_performance_reviews_3_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1670,7 +1670,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>job_performance_ratings_choices</t>
+          <t>job_performance_ratings_2_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1687,7 +1687,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>job_performance_ratings_choices</t>
+          <t>job_performance_ratings_2_choices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
